--- a/public/static/出入库导入模板.xlsx
+++ b/public/static/出入库导入模板.xlsx
@@ -4,18 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="出入库导入模板" sheetId="1" r:id="rId1"/>
     <sheet name="示例" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>序号</t>
   </si>
@@ -53,6 +66,19 @@
   </si>
   <si>
     <r>
+      <t>数量(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必填</t>
+    </r>
+    <r>
       <rPr>
         <b/>
         <sz val="12"/>
@@ -60,6 +86,120 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>含税单价(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必填</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>税率(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必填</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>货位编码</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产品图号(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>必填</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>数量(</t>
     </r>
     <r>
@@ -85,7 +225,14 @@
   </si>
   <si>
     <r>
-      <t>含税单价（</t>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单价（</t>
     </r>
     <r>
       <rPr>
@@ -141,77 +288,7 @@
     </r>
   </si>
   <si>
-    <t>货位编码</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>产品图号(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>必填</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单价（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>必填</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
   </si>
   <si>
     <r>
@@ -301,14 +378,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -503,6 +580,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1575,9 +1659,7 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -1656,16 +1738,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
@@ -1676,64 +1758,64 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7">
       <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3"/>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5">
         <v>500</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" s="3"/>
     </row>
